--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-19.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-19.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;Kč&quot;;-#,##0 &quot;Kč&quot;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +95,10 @@
     <font>
       <b val="1"/>
       <color rgb="00A04000"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -254,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -306,10 +310,13 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -324,7 +331,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -333,10 +340,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1078,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>4 WebSearch verified (2.1 %) ✓ | 9 wrong leaf flagged (4.8 %) ⚠ | 176 needs_production_lookup (93.1 %)</t>
+          <t>6 WebSearch verified (3.2 %) ✓ | 9 wrong leaf flagged (4.8 %) ⚠ | 174 needs_production_lookup (92.1 %)</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1950,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2094,7 +2101,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Hloubení figury anglický dvorek — Hloubení figury pro anglický dvorek a nový vstup do 1.PP ze zahrady</t>
+          <t>Hloubení figury anglický dvorek — Hloubení jam nezapažených pro anglický dvorek a nový vstup do 1.PP ze zahrady, hornina tř. 3 (F4-CS)</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
@@ -2114,7 +2121,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 132211101</t>
+          <t>URS-prop 131201101</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2281,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>URS-prop None</t>
+          <t>URS-prop 162701??? ?</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2381,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Hloubení figury skladu — Hloubení figury pro objekt skladu v lichoběžníku 6.35 × 3.34 m, hl. do 1.2 m</t>
+          <t>Hloubení figury skladu — Hloubení jam nezapažených pro objekt skladu v lichoběžníku 6,35 × 3,34 m, hl. do 1,2 m, hornina tř. 3</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -2394,7 +2401,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 132211101</t>
+          <t>URS-prop 131201101</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2561,7 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>URS-prop None</t>
+          <t>URS-prop 162701??? ?</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2761,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>URS-prop None</t>
+          <t>URS-prop 711141??? ?</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3121,7 @@
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>URS-prop None</t>
+          <t>URS-prop 271313??? ?</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5241,7 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>URS-prop None</t>
+          <t>URS-prop 762??? ?</t>
         </is>
       </c>
     </row>
@@ -6609,12 +6616,12 @@
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>132211101</t>
+          <t>131201101</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Hloubení figury pro anglický dvorek a nový vstup do 1.PP ze zahrady</t>
+          <t>Hloubení jam nezapažených pro anglický dvorek a nový vstup do 1.PP ze zahrady, hornina tř. 3 (F4-CS)</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
@@ -6637,7 +6644,7 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
@@ -6650,9 +6657,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6866,11 @@
           <t>Odvoz výkopu</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n"/>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>162701??? ?</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Vodorovné přemístění výkopku — odvoz na deponii do 8 km vč. skládkovného (zemina F4)</t>
@@ -6897,7 +6908,7 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -7232,7 +7243,11 @@
           <t>Bílá vana — separační fólie</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n"/>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>711141??? ?</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Separační PE fólie pod základovou patou bílé vany (povinná dle ČBS 02)</t>
@@ -7271,7 +7286,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O14" s="27" t="inlineStr">
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -10189,7 +10204,11 @@
           <t>Bourání plechové střešní krytiny</t>
         </is>
       </c>
-      <c r="D61" s="20" t="n"/>
+      <c r="D61" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
           <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
@@ -10228,7 +10247,7 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O61" s="27" t="inlineStr">
+      <c r="O61" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -11382,7 +11401,11 @@
           <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
         </is>
       </c>
-      <c r="D80" s="20" t="n"/>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
           <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
@@ -11421,7 +11444,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="O80" s="27" t="inlineStr">
+      <c r="O80" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -11441,7 +11464,11 @@
           <t>Podlahový EPS 150</t>
         </is>
       </c>
-      <c r="D81" s="20" t="n"/>
+      <c r="D81" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
           <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
@@ -11480,7 +11507,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="O81" s="27" t="inlineStr">
+      <c r="O81" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -11500,7 +11527,11 @@
           <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
-      <c r="D82" s="20" t="n"/>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
@@ -11539,7 +11570,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O82" s="27" t="inlineStr">
+      <c r="O82" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -16844,12 +16875,12 @@
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>132211101</t>
+          <t>131201101</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Hloubení figury pro objekt skladu v lichoběžníku 6.35 × 3.34 m, hl. do 1.2 m</t>
+          <t>Hloubení jam nezapažených pro objekt skladu v lichoběžníku 6,35 × 3,34 m, hl. do 1,2 m, hornina tř. 3</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
@@ -16872,7 +16903,7 @@
       </c>
       <c r="L3" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -16885,9 +16916,9 @@
           <t>#18</t>
         </is>
       </c>
-      <c r="O3" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O3" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17125,11 @@
           <t>Odvoz výkopu sklad</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n"/>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>162701??? ?</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Odvoz výkopku z hloubení skladu + figur + patek na deponii do 8 km</t>
@@ -17132,7 +17167,7 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -17152,7 +17187,11 @@
           <t>Základové pasy sklad</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n"/>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>271313??? ?</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
@@ -17191,7 +17230,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -18156,7 +18195,11 @@
           <t>Betonová dlažba sklad</t>
         </is>
       </c>
-      <c r="D24" s="20" t="n"/>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
@@ -18195,7 +18238,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O24" s="27" t="inlineStr">
+      <c r="O24" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -18489,14 +18532,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>VÝKAZ VÝMĚR — PER PODLAŽÍ + PER MÍSTNOST + AUDIT TRAIL (hk212-style)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Per-místnost data z DXF tabulky místností (km_tabulka místností MTEXT); per-item formula audit trail ukazuje 'co s čím se sčítalo a násobilo'</t>
         </is>
@@ -19406,7 +19449,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>1.NP</t>
         </is>
@@ -19427,7 +19470,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>1.PP</t>
         </is>
@@ -19448,7 +19491,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>2.NP</t>
         </is>
@@ -19469,7 +19512,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>3.NP</t>
         </is>
@@ -19498,14 +19541,14 @@
       <c r="B38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="C38" s="31" t="n">
+      <c r="C38" s="32" t="n">
         <v>217.5</v>
       </c>
       <c r="D38" s="8">
         <f> součet 4 podlaží | TZ baseline: 219.3 m² | Δ = -1.8 m² (-0.82 %)</f>
         <v/>
       </c>
-      <c r="E38" s="32" t="n"/>
+      <c r="E38" s="33" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -19701,14 +19744,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>VÝKAZ SKLADEB VRSTEV — TZ-EXPLICIT COMPOSITION PER ELEMENT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>Skladby vrstev pochází VÝHRADNĚ z TZ explicit text (ARS dum + statika dum + B souhrnná + PBŘ TUSPO). DXF cross-validation slouží pouze jako podpůrný důkaz přes semantic HATCH patterns (CONCRETE1 = ŽB, INSULATION = EPS/MW, WOOD3 = dřevo). ŽÁDNÝ generic 'standard RD' pattern. Kde TZ silent, explicit '_TZ_silent' flag s ČSN fallback.</t>
         </is>
@@ -19752,12 +19795,12 @@
       </c>
     </row>
     <row r="5" ht="176" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>S01 — obvodová stěna omítka (1.NP, 2.NP, suterén nad terénem)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>1. Povrch dle tabulky místností (výmalba / obklad)
 2. Vnitřní omítka (tl. 10-15 mm)
@@ -19772,39 +19815,39 @@
 11.   • Tenkovrstvá probarvená silikonová omítka (tl. 2 mm)</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda 'S01 obvodová stěna - omítka'</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>External perimeter 38.70 m (DXF km_R_návrh_tlustá 2)</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="37" t="inlineStr">
+      <c r="F5" s="38" t="inlineStr">
         <is>
           <t>276.7 m²</t>
         </is>
       </c>
-      <c r="G5" s="38" t="inlineStr">
+      <c r="G5" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>S02 — obvodová stěna společná řadového domu (štítová)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>1. Výmalba
 2. Vnitřní omítka (tl. 10-15 mm)
@@ -19812,39 +19855,39 @@
 4. Vnitřní omítka (druhá strana) (tl. 10-15 mm)</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S02</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
+      <c r="F6" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="38" t="inlineStr">
+      <c r="G6" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="7" ht="144" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>S03 — suterénní stěna (1.PP)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>1. Vnitřní omítka (tl. 10-15 mm)
 2. Smíšené zdivo - cihla plná (keramická) (tl. 600 mm)
@@ -19857,39 +19900,39 @@
 9. S03b: keramický obklad (tl. 20 mm)</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S03 + S03a + S03b</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="38" t="inlineStr">
+      <c r="G7" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>S04 — podlaha na terénu v suterénu</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>1. Epoxidová stěrka
 2. Penetrace podkladu
@@ -19898,39 +19941,39 @@
 5. Rostlý terén / zemina</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S04</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>1.PP (0.01..0.04 — sklep, technic, sušárna)</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>32.4 m²</t>
         </is>
       </c>
-      <c r="G8" s="38" t="inlineStr">
+      <c r="G8" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="9" ht="144" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>S05 — podlaha na terénu v přízemí (1.NP)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>1. Nášlapná vrstva dle tabulky místností (vinyl / dlažba) (tl. 15 mm)
 2. Samonivelační stěrka (tl. cca 5 mm)
@@ -19943,39 +19986,39 @@
 9. Zhutněný terén</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S05 + TZ ARS §3.2.4 confirms</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>1.NP (1.01..1.08)</t>
         </is>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>59.5 m²</t>
         </is>
       </c>
-      <c r="G9" s="38" t="inlineStr">
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>S06 — strop klenba mezi suterénem a přízemím</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>1. Nášlapná vrstva (tl. 20 mm)
 2. Hustá perlitbetonová plastická hmota TB2 (tl. 50 mm)
@@ -19985,39 +20028,39 @@
 6. Výmalba</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S06</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="37" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>50 m²</t>
         </is>
       </c>
-      <c r="G10" s="38" t="inlineStr">
+      <c r="G10" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>S07 — strop trámový mezi 1.NP a 2.NP</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>1. Nášlapná vrstva (tl. 20 mm)
 2. Roznášecí vrstva - sádrovláknité dílce (př. Fermacell 2E22) (tl. 25 mm)
@@ -20031,39 +20074,39 @@
 10. Výmalba</t>
         </is>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S07</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="37" t="inlineStr">
+      <c r="F11" s="38" t="inlineStr">
         <is>
           <t>59.5 m²</t>
         </is>
       </c>
-      <c r="G11" s="38" t="inlineStr">
+      <c r="G11" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="12" ht="112" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>S08 — strop cihelná klenba mezi patry</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>1. Nášlapná vrstva (tl. 20 mm)
 2. Roznášecí vrstva sádrovláknité dílce (Fermacell 2E22) (tl. 25 mm)
@@ -20074,39 +20117,39 @@
 7. Výmalba</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S08</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="37" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="38" t="inlineStr">
+      <c r="G12" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="13" ht="144" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>S09 — strop ocelobeton mezi 2.NP a 3.NP (košický plech)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>1. Nivelace + nášlapná vrstva (tl. 40 mm)
 2. Betonová mazanina s kari sítí (tl. 60 mm)
@@ -20119,39 +20162,39 @@
 9. Výmalba</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S09 + statika §4 confirms IPE180+HEA180/200</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="37" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>104.4 m²</t>
         </is>
       </c>
-      <c r="G13" s="38" t="inlineStr">
+      <c r="G13" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="14" ht="160" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>S10 — šikmá střecha (krov nadkrokevní)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>1. Hliníková falcovaná krytina, pásy cca 500 mm
 2. Pojistná hydroizolační folie pod hliníkovou krytinu
@@ -20165,76 +20208,76 @@
 10. Krokve (tl. 180 mm)</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S10 + TZ ARS §3.2.3</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="37" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>141 m²</t>
         </is>
       </c>
-      <c r="G14" s="38" t="inlineStr">
+      <c r="G14" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>S11 — lehký strop vloženého mezipatra (biodeska)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>1. Dřevěná biodeska osazená pružně na kleštiny</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S11</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="37" t="inlineStr">
+      <c r="F15" s="38" t="inlineStr">
         <is>
           <t>25 m²</t>
         </is>
       </c>
-      <c r="G15" s="38" t="inlineStr">
+      <c r="G15" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="16" ht="160" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>S12a — obvodová stěna podkroví, fasáda omítka</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>1. Povrch dle tabulky místností (výmalba, obklad)
 2. Vnitřní omítka sádrová stříkaná (tl. 10-15 mm)
@@ -20248,39 +20291,39 @@
 10.   • Tenkovrstvá probarvená silikonová omítka (tl. 2 mm)</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S12 + S12a</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="37" t="inlineStr">
+      <c r="F16" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="38" t="inlineStr">
+      <c r="G16" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
       </c>
     </row>
     <row r="17" ht="144" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>S12b — obvodová stěna podkroví, fasáda falcovaný plech (provětrávaná)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>1. Povrch interier dle tabulky místností (výmalba, obklad)
 2. Vnitřní omítka sádrová stříkaná (tl. 10-15 mm)
@@ -20293,27 +20336,27 @@
 9.   • Hliníková falcovaná krytina, pásy cca 500 mm</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>PDF řez D.1.1.2.2.21 — legenda S12b</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="37" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>24 m²</t>
         </is>
       </c>
-      <c r="G17" s="38" t="inlineStr">
+      <c r="G17" s="39" t="inlineStr">
         <is>
           <t>TZ explicit</t>
         </is>
@@ -20334,14 +20377,14 @@
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>⚠ Per-podlaží výška: TZ NEMÁ explicit value. Fallback: 1.PP 2.50 m, 1.NP 2.80 m, 2.NP 2.80 m, 3.NP nadezdívka 2.65 m. Σ = 10.75 m vs TZ B 13.0 m celková výška = +2.25 m pro krov+střechu. Flag: tz_silent_fallback_csn_vyska_podlazi.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>⚠ Obklad výška v koupelnách: TZ NEMÁ explicit value. Fallback: 2.0 m (CSN Czech RD standard, po sprchový kout). Flag: tz_silent_fallback_csn_obklad_vyska_2m.</t>
         </is>
@@ -20366,7 +20409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20511,7 +20554,7 @@
           <t>162701105</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf (distance)</t>
         </is>
@@ -20553,7 +20596,7 @@
           <t>711132101</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf (material)</t>
         </is>
@@ -20595,7 +20638,7 @@
           <t>962081141</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_work_type</t>
         </is>
@@ -20637,7 +20680,7 @@
           <t>771121011</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_work_type</t>
         </is>
@@ -20847,7 +20890,7 @@
           <t>713141121</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_location</t>
         </is>
@@ -20889,7 +20932,7 @@
           <t>273313811</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_geometry</t>
         </is>
@@ -20925,25 +20968,63 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>131201101</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>✓ correct_replacement</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.003, 260217_sklad.HSV1.002</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Hloubení jam nezapažených v hornině tř. 3 objemu do 100 m3</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Hloubení jam nezapažených pro anglický dvorek a nový vstup do 1.PP ze zahrady, h…</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Korekce 2026-05-19: items.json měly fabrikovaný term 'Hloubení figury' (RU loanword) + špatný 6-digit family 132 (rýhy). Item je ve skutečnosti JAMY (TKP 131) — anglický dvorek + objekt skladu = bodové výkopové práce, ne lineární. Popis přepsán + kód změněn na verifikovaný 131201101.</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>0.95–0.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Zdroj: outputs/urs_websearch_verifications.json (12 WebSearch queries 2026-05-18).
 Metoda: podminky.urs.cz blokuje WebFetch (403), ale Google indexuje stejný obsah přes veřejné zrcadla českých veřejných zakázek (smlouvy.gov.cz, vhodne-uverejneni.cz, docplayer.cz, cs-urs.cz). WebSearch tool agreguje 10 snippet linků + LLM summary extrahuje URS popis when anchored.
 Key finding: heuristic urs_code_proposed v phase1_items_generator.py odhadne první 6 cifer (rodinu) správně v ~75 % případů, ale 9-cifrový leaf je chybný v ~63 % verified codes.</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="H16" s="16" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n"/>
@@ -20954,19 +21035,23 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="19" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="H19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H14"/>
   <mergeCells count="1">
-    <mergeCell ref="A15:H19"/>
+    <mergeCell ref="A16:H20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-19.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-19.xlsx
@@ -20,8 +20,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>6 WebSearch verified (3.2 %) ✓ | 9 wrong leaf flagged (4.8 %) ⚠ | 174 needs_production_lookup (92.1 %)</t>
+          <t>8 WebSearch verified (3.8 %) ✓ | 9 wrong leaf flagged (4.3 %) ⚠ | 191 needs_production_lookup (91.8 %)</t>
         </is>
       </c>
     </row>
@@ -1160,8 +1160,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-189 položek celkem (162 dum + 27 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 25×0.95 · 23×0.90 · 39×0.85 · 16×0.80 · 69×0.75.
+208 položek celkem (181 dum + 27 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 28×0.95 · 34×0.90 · 43×0.85 · 17×0.80 · 69×0.75.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1426,11 +1426,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+8 dalších)</t>
+          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+11 dalších)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -1526,11 +1526,11 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+6 dalších)</t>
+          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+16 dalších)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+8 dalších)</t>
+          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
@@ -1676,11 +1676,11 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+11 dalších)</t>
+          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+12 dalších)</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
@@ -1938,7 +1938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5891,37 +5891,37 @@
       </c>
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
-        </is>
-      </c>
-      <c r="C99" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -5931,37 +5931,37 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
-        </is>
-      </c>
-      <c r="C100" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -5971,37 +5971,37 @@
       </c>
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
-        </is>
-      </c>
-      <c r="C101" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F101" s="23" t="n">
+        <v>15</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -6011,17 +6011,17 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 10 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+7 dalších)</t>
+          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 20 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+17 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 12 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+9 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 15 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+12 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -6365,8 +6365,128 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C111" s="21" t="inlineStr">
+        <is>
+          <t>PSV-78 — Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+        </is>
+      </c>
+      <c r="E111" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="10" t="n"/>
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J111" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C112" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 16 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+13 dalších)</t>
+        </is>
+      </c>
+      <c r="E113" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6377,7 +6497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O163"/>
+  <dimension ref="A1:O182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10889,50 +11009,50 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="n">
-        <v>276.7</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="10" t="n"/>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K72" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L72" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
@@ -10940,9 +11060,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O72" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O72" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
     </row>
@@ -10952,50 +11072,50 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="n">
-        <v>276.7</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K73" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
@@ -11003,9 +11123,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O73" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O73" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
     </row>
@@ -11015,41 +11135,41 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="n">
-        <v>13.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="n">
+        <v>15</v>
       </c>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="n"/>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K74" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L74" s="20" t="inlineStr">
         <is>
@@ -11058,12 +11178,12 @@
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O74" s="26" t="inlineStr">
@@ -11083,26 +11203,26 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G75" s="22" t="n">
-        <v>82.2</v>
+        <v>276.7</v>
       </c>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
@@ -11112,7 +11232,7 @@
         </is>
       </c>
       <c r="K75" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L75" s="20" t="inlineStr">
         <is>
@@ -11121,12 +11241,12 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O75" s="26" t="inlineStr">
@@ -11146,26 +11266,26 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
@@ -11175,7 +11295,7 @@
         </is>
       </c>
       <c r="K76" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L76" s="20" t="inlineStr">
         <is>
@@ -11184,12 +11304,12 @@
       </c>
       <c r="M76" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O76" s="26" t="inlineStr">
@@ -11209,17 +11329,17 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
@@ -11228,7 +11348,7 @@
         </is>
       </c>
       <c r="G77" s="22" t="n">
-        <v>290.2</v>
+        <v>13.5</v>
       </c>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="10" t="n"/>
@@ -11247,7 +11367,7 @@
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
@@ -11267,41 +11387,41 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G78" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="10" t="n"/>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K78" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L78" s="20" t="inlineStr">
         <is>
@@ -11310,12 +11430,12 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O78" s="26" t="inlineStr">
@@ -11330,41 +11450,41 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>712381111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="n">
-        <v>12</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K79" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
@@ -11373,7 +11493,7 @@
       </c>
       <c r="M79" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N79" s="20" t="inlineStr">
@@ -11393,22 +11513,22 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
-        </is>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>711??? ?</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -11417,36 +11537,36 @@
         </is>
       </c>
       <c r="G80" s="22" t="n">
-        <v>40.5</v>
+        <v>290.2</v>
       </c>
       <c r="H80" s="10" t="n"/>
       <c r="I80" s="10" t="n"/>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K80" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L80" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="O80" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -11456,22 +11576,22 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
-        </is>
-      </c>
-      <c r="D81" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>HI pod ŽB deskou 1.NP</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -11480,13 +11600,13 @@
         </is>
       </c>
       <c r="G81" s="22" t="n">
-        <v>177.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K81" s="24" t="n">
@@ -11494,22 +11614,22 @@
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="O81" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="O81" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -11519,50 +11639,50 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D82" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Odvětrání radonu z podloží</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G82" s="22" t="n">
-        <v>104.4</v>
+        <v>12</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
@@ -11570,9 +11690,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O82" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O82" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -11582,60 +11702,60 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
-        </is>
-      </c>
-      <c r="D83" s="20" t="inlineStr">
-        <is>
-          <t>764312235</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D83" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G83" s="22" t="n">
-        <v>69.5</v>
+        <v>40.5</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K83" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L83" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="O83" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="O83" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
     </row>
@@ -11645,60 +11765,60 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
-        </is>
-      </c>
-      <c r="D84" s="20" t="inlineStr">
-        <is>
-          <t>764218201</t>
+          <t>Podlahový EPS 150</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G84" s="22" t="n">
-        <v>20.8</v>
+        <v>177.5</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="O84" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
     </row>
@@ -11708,50 +11828,50 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
-        </is>
-      </c>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>764454802</t>
+          <t>Kročejová EPS nad ocelobeton</t>
+        </is>
+      </c>
+      <c r="D85" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G85" s="22" t="n">
-        <v>43.5</v>
+        <v>104.4</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
@@ -11759,9 +11879,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O85" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O85" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
     </row>
@@ -11776,17 +11896,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Oplechování krytiny</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
@@ -11795,7 +11915,7 @@
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>26.1</v>
+        <v>69.5</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -11814,12 +11934,12 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O86" s="26" t="inlineStr">
@@ -11834,41 +11954,41 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="n">
-        <v>16</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="n">
+        <v>20.8</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
@@ -11877,7 +11997,7 @@
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
@@ -11897,41 +12017,41 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>771474112</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>30</v>
+        <v>43.5</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L88" s="20" t="inlineStr">
         <is>
@@ -11940,7 +12060,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP)</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -11960,41 +12080,41 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>26.1</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K89" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
@@ -12003,12 +12123,12 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O89" s="26" t="inlineStr">
@@ -12023,22 +12143,22 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -12047,17 +12167,17 @@
         </is>
       </c>
       <c r="G90" s="23" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L90" s="20" t="inlineStr">
         <is>
@@ -12066,12 +12186,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -12086,41 +12206,41 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Terasa garapa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>771474112</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="n">
-        <v>4</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>30</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -12129,12 +12249,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP)</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -12154,7 +12274,7 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -12164,7 +12284,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -12173,7 +12293,7 @@
         </is>
       </c>
       <c r="G92" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="10" t="n"/>
@@ -12192,7 +12312,7 @@
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -12217,7 +12337,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -12227,7 +12347,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -12236,7 +12356,7 @@
         </is>
       </c>
       <c r="G93" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -12255,7 +12375,7 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
@@ -12280,7 +12400,7 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -12290,7 +12410,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
@@ -12299,7 +12419,7 @@
         </is>
       </c>
       <c r="G94" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -12318,7 +12438,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
@@ -12343,7 +12463,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -12353,7 +12473,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
@@ -12362,7 +12482,7 @@
         </is>
       </c>
       <c r="G95" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -12381,7 +12501,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -12406,17 +12526,17 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -12425,17 +12545,17 @@
         </is>
       </c>
       <c r="G96" s="23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
@@ -12444,7 +12564,7 @@
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
@@ -12469,17 +12589,17 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -12488,7 +12608,7 @@
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -12498,7 +12618,7 @@
         </is>
       </c>
       <c r="K97" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
@@ -12507,12 +12627,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -12532,17 +12652,17 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
@@ -12551,17 +12671,17 @@
         </is>
       </c>
       <c r="G98" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K98" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L98" s="20" t="inlineStr">
         <is>
@@ -12570,7 +12690,7 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
@@ -12590,41 +12710,41 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -12633,7 +12753,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -12653,41 +12773,41 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G100" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -12696,7 +12816,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -12716,22 +12836,22 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -12740,13 +12860,13 @@
         </is>
       </c>
       <c r="G101" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K101" s="24" t="n">
@@ -12759,12 +12879,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -12779,41 +12899,41 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>18</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -12822,7 +12942,7 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
@@ -12842,37 +12962,37 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>171.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K103" s="24" t="n">
@@ -12885,12 +13005,12 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O103" s="26" t="inlineStr">
@@ -12905,41 +13025,41 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G104" s="22" t="n">
-        <v>13.5</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -12948,12 +13068,12 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O104" s="26" t="inlineStr">
@@ -12968,41 +13088,41 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>32.4</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L105" s="20" t="inlineStr">
         <is>
@@ -13011,12 +13131,12 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O105" s="26" t="inlineStr">
@@ -13031,37 +13151,37 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>25</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
@@ -13074,12 +13194,12 @@
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O106" s="26" t="inlineStr">
@@ -13094,41 +13214,41 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G107" s="22" t="n">
-        <v>126.4</v>
+        <v>18</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
@@ -13137,12 +13257,12 @@
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O107" s="26" t="inlineStr">
@@ -13162,26 +13282,26 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G108" s="22" t="n">
-        <v>72.03</v>
+        <v>171.5</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
@@ -13200,12 +13320,12 @@
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -13225,26 +13345,26 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G109" s="22" t="n">
-        <v>19.28</v>
+        <v>13.5</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -13263,12 +13383,12 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O109" s="26" t="inlineStr">
@@ -13283,22 +13403,22 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -13307,17 +13427,17 @@
         </is>
       </c>
       <c r="G110" s="22" t="n">
-        <v>78.2</v>
+        <v>32.4</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K110" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L110" s="20" t="inlineStr">
         <is>
@@ -13326,12 +13446,12 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O110" s="26" t="inlineStr">
@@ -13346,22 +13466,22 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -13370,17 +13490,17 @@
         </is>
       </c>
       <c r="G111" s="22" t="n">
-        <v>208.4</v>
+        <v>25</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K111" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L111" s="20" t="inlineStr">
         <is>
@@ -13389,7 +13509,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -13409,22 +13529,22 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -13433,17 +13553,17 @@
         </is>
       </c>
       <c r="G112" s="22" t="n">
-        <v>201.6</v>
+        <v>126.4</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K112" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L112" s="20" t="inlineStr">
         <is>
@@ -13452,12 +13572,12 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O112" s="26" t="inlineStr">
@@ -13472,41 +13592,41 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G113" s="22" t="n">
-        <v>179.1</v>
+        <v>72.03</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K113" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
@@ -13515,12 +13635,12 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O113" s="26" t="inlineStr">
@@ -13535,37 +13655,37 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G114" s="22" t="n">
-        <v>59.5</v>
+        <v>19.28</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K114" s="24" t="n">
@@ -13578,7 +13698,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -13603,17 +13723,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -13622,17 +13742,17 @@
         </is>
       </c>
       <c r="G115" s="22" t="n">
-        <v>61.1</v>
+        <v>78.2</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -13641,12 +13761,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -13666,17 +13786,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -13685,17 +13805,17 @@
         </is>
       </c>
       <c r="G116" s="22" t="n">
-        <v>64.5</v>
+        <v>208.4</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -13704,12 +13824,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -13729,17 +13849,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -13748,13 +13868,13 @@
         </is>
       </c>
       <c r="G117" s="22" t="n">
-        <v>13.4</v>
+        <v>201.6</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
@@ -13767,12 +13887,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -13792,17 +13912,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -13811,13 +13931,13 @@
         </is>
       </c>
       <c r="G118" s="22" t="n">
-        <v>15.2</v>
+        <v>179.1</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
@@ -13830,12 +13950,12 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O118" s="26" t="inlineStr">
@@ -13855,17 +13975,17 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -13874,17 +13994,17 @@
         </is>
       </c>
       <c r="G119" s="22" t="n">
-        <v>24.3</v>
+        <v>59.5</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -13893,7 +14013,7 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
@@ -13918,17 +14038,17 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -13937,13 +14057,13 @@
         </is>
       </c>
       <c r="G120" s="22" t="n">
-        <v>10</v>
+        <v>61.1</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K120" s="24" t="n">
@@ -13956,7 +14076,7 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
@@ -13981,17 +14101,17 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -14000,17 +14120,17 @@
         </is>
       </c>
       <c r="G121" s="22" t="n">
-        <v>577.9</v>
+        <v>64.5</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K121" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L121" s="20" t="inlineStr">
         <is>
@@ -14019,7 +14139,7 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -14039,41 +14159,41 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G122" s="23" t="n">
-        <v>4</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>13.4</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K122" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L122" s="20" t="inlineStr">
         <is>
@@ -14082,7 +14202,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -14102,41 +14222,41 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G123" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>15.2</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
@@ -14145,7 +14265,7 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
@@ -14165,41 +14285,41 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G124" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G124" s="22" t="n">
+        <v>24.3</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
@@ -14208,12 +14328,12 @@
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O124" s="26" t="inlineStr">
@@ -14228,41 +14348,41 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="n">
-        <v>4</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G125" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K125" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L125" s="20" t="inlineStr">
         <is>
@@ -14271,12 +14391,12 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O125" s="26" t="inlineStr">
@@ -14291,41 +14411,41 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -14334,12 +14454,12 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O126" s="26" t="inlineStr">
@@ -14354,41 +14474,41 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G127" s="23" t="n">
-        <v>70</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>254.5</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -14397,12 +14517,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -14417,41 +14537,41 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G128" s="23" t="n">
-        <v>35</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="n">
+        <v>78.2</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K128" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L128" s="20" t="inlineStr">
         <is>
@@ -14460,12 +14580,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -14480,37 +14600,37 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G129" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G129" s="22" t="n">
+        <v>247.5</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K129" s="24" t="n">
@@ -14523,12 +14643,12 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O129" s="26" t="inlineStr">
@@ -14543,41 +14663,41 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G130" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G130" s="22" t="n">
+        <v>219.3</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -14586,7 +14706,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -14606,37 +14726,37 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G131" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K131" s="24" t="n">
@@ -14649,12 +14769,12 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O131" s="26" t="inlineStr">
@@ -14669,41 +14789,41 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G132" s="22" t="n">
-        <v>80</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G132" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K132" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L132" s="20" t="inlineStr">
         <is>
@@ -14712,12 +14832,12 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O132" s="26" t="inlineStr">
@@ -14732,41 +14852,41 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G133" s="22" t="n">
-        <v>60</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G133" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K133" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L133" s="20" t="inlineStr">
         <is>
@@ -14775,12 +14895,12 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O133" s="26" t="inlineStr">
@@ -14795,41 +14915,41 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G134" s="22" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K134" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L134" s="20" t="inlineStr">
         <is>
@@ -14838,12 +14958,12 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O134" s="26" t="inlineStr">
@@ -14858,41 +14978,41 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
@@ -14901,12 +15021,12 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O135" s="26" t="inlineStr">
@@ -14921,41 +15041,41 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G136" s="22" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K136" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L136" s="20" t="inlineStr">
         <is>
@@ -14964,12 +15084,12 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O136" s="26" t="inlineStr">
@@ -14984,22 +15104,22 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -15008,17 +15128,17 @@
         </is>
       </c>
       <c r="G137" s="23" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L137" s="20" t="inlineStr">
         <is>
@@ -15027,12 +15147,12 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O137" s="26" t="inlineStr">
@@ -15047,41 +15167,41 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K138" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L138" s="20" t="inlineStr">
         <is>
@@ -15090,12 +15210,12 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O138" s="26" t="inlineStr">
@@ -15110,27 +15230,27 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G139" s="23" t="n">
@@ -15140,11 +15260,11 @@
       <c r="I139" s="10" t="n"/>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K139" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L139" s="20" t="inlineStr">
         <is>
@@ -15153,12 +15273,12 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O139" s="26" t="inlineStr">
@@ -15178,22 +15298,22 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G140" s="23" t="n">
@@ -15216,7 +15336,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -15236,41 +15356,41 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G141" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G141" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -15279,7 +15399,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -15299,37 +15419,37 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G142" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G142" s="22" t="n">
+        <v>60</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K142" s="24" t="n">
@@ -15342,12 +15462,12 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O142" s="26" t="inlineStr">
@@ -15362,41 +15482,41 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G143" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -15405,7 +15525,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -15425,22 +15545,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -15455,11 +15575,11 @@
       <c r="I144" s="10" t="n"/>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K144" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L144" s="20" t="inlineStr">
         <is>
@@ -15468,12 +15588,12 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O144" s="26" t="inlineStr">
@@ -15488,22 +15608,22 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -15518,11 +15638,11 @@
       <c r="I145" s="10" t="n"/>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K145" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L145" s="20" t="inlineStr">
         <is>
@@ -15531,12 +15651,12 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O145" s="26" t="inlineStr">
@@ -15551,22 +15671,22 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -15575,17 +15695,17 @@
         </is>
       </c>
       <c r="G146" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K146" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
@@ -15594,12 +15714,12 @@
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O146" s="26" t="inlineStr">
@@ -15614,41 +15734,41 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G147" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
@@ -15657,7 +15777,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -15677,41 +15797,41 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G148" s="22" t="n">
-        <v>100</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -15720,12 +15840,12 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O148" s="26" t="inlineStr">
@@ -15740,27 +15860,27 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -15770,11 +15890,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -15783,12 +15903,12 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O149" s="26" t="inlineStr">
@@ -15803,27 +15923,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -15833,11 +15953,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -15846,7 +15966,7 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
@@ -15866,41 +15986,41 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="n">
-        <v>7</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -15909,12 +16029,12 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O151" s="26" t="inlineStr">
@@ -15929,27 +16049,27 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G152" s="23" t="n">
@@ -15959,11 +16079,11 @@
       <c r="I152" s="10" t="n"/>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -15972,12 +16092,12 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O152" s="26" t="inlineStr">
@@ -15992,41 +16112,41 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G153" s="22" t="n">
-        <v>56.9</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K153" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L153" s="20" t="inlineStr">
         <is>
@@ -16035,12 +16155,12 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O153" s="26" t="inlineStr">
@@ -16055,41 +16175,41 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K154" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L154" s="20" t="inlineStr">
         <is>
@@ -16098,7 +16218,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -16118,41 +16238,41 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -16161,12 +16281,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -16181,41 +16301,41 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G156" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H156" s="10" t="n"/>
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -16224,12 +16344,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -16244,27 +16364,27 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G157" s="23" t="n">
@@ -16274,11 +16394,11 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
@@ -16287,12 +16407,12 @@
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -16307,27 +16427,27 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum stávajícího krovu a dřevěných trámů zhlaví — provádí autorizovaný mykolog při bourání</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G158" s="23" t="n">
@@ -16337,7 +16457,7 @@
       <c r="I158" s="10" t="n"/>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K158" s="24" t="n">
@@ -16350,12 +16470,12 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — explicitně mykologický průzkum</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O158" s="26" t="inlineStr">
@@ -16370,27 +16490,27 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G159" s="23" t="n">
@@ -16400,7 +16520,7 @@
       <c r="I159" s="10" t="n"/>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K159" s="24" t="n">
@@ -16413,12 +16533,12 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O159" s="26" t="inlineStr">
@@ -16433,22 +16553,22 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
@@ -16463,11 +16583,11 @@
       <c r="I160" s="10" t="n"/>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -16476,7 +16596,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -16496,41 +16616,41 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G161" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -16539,12 +16659,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -16559,41 +16679,41 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G162" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H162" s="10" t="n"/>
       <c r="I162" s="10" t="n"/>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K162" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L162" s="20" t="inlineStr">
         <is>
@@ -16602,12 +16722,12 @@
       </c>
       <c r="M162" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N162" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O162" s="26" t="inlineStr">
@@ -16622,27 +16742,27 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G163" s="23" t="n">
@@ -16652,36 +16772,1233 @@
       <c r="I163" s="10" t="n"/>
       <c r="J163" s="8" t="inlineStr">
         <is>
+          <t>specialista_TC_multisplit</t>
+        </is>
+      </c>
+      <c r="K163" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L163" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M163" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+        </is>
+      </c>
+      <c r="N163" s="20" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="O163" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>PSV-73 Vytápění</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>Multisplit TČ — vnitřní jednotky</t>
+        </is>
+      </c>
+      <c r="D164" s="20" t="inlineStr">
+        <is>
+          <t>733425221</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H164" s="10" t="n"/>
+      <c r="I164" s="10" t="n"/>
+      <c r="J164" s="8" t="inlineStr">
+        <is>
+          <t>specialista_TC_multisplit</t>
+        </is>
+      </c>
+      <c r="K164" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L164" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M164" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+        </is>
+      </c>
+      <c r="N164" s="20" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="O164" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>PSV-73 Vytápění</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>Revize komínu</t>
+        </is>
+      </c>
+      <c r="D165" s="20" t="inlineStr">
+        <is>
+          <t>734262122</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+        </is>
+      </c>
+      <c r="F165" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="10" t="n"/>
+      <c r="I165" s="10" t="n"/>
+      <c r="J165" s="8" t="inlineStr">
+        <is>
+          <t>kominik</t>
+        </is>
+      </c>
+      <c r="K165" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L165" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M165" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+        </is>
+      </c>
+      <c r="N165" s="20" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="O165" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>PSV-73 Vytápění</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>Rozvody otopné soustavy</t>
+        </is>
+      </c>
+      <c r="D166" s="20" t="inlineStr">
+        <is>
+          <t>733111021</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+        </is>
+      </c>
+      <c r="F166" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G166" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H166" s="10" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="8" t="inlineStr">
+        <is>
+          <t>topenar</t>
+        </is>
+      </c>
+      <c r="K166" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L166" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M166" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+        </is>
+      </c>
+      <c r="N166" s="20" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="O166" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>VRN — BOZP</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>Koordinace BOZP</t>
+        </is>
+      </c>
+      <c r="D167" s="20" t="inlineStr">
+        <is>
+          <t>030091000</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+        </is>
+      </c>
+      <c r="F167" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G167" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="10" t="n"/>
+      <c r="I167" s="10" t="n"/>
+      <c r="J167" s="8" t="inlineStr">
+        <is>
           <t>VRN_management</t>
         </is>
       </c>
-      <c r="K163" s="24" t="n">
+      <c r="K167" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L167" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M167" s="8" t="inlineStr">
+        <is>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+        </is>
+      </c>
+      <c r="N167" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O167" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Dokumentace</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>Předávací protokoly + DSP</t>
+        </is>
+      </c>
+      <c r="D168" s="20" t="inlineStr">
+        <is>
+          <t>030151000</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
+        <is>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+        </is>
+      </c>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="10" t="n"/>
+      <c r="I168" s="10" t="n"/>
+      <c r="J168" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K168" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L168" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M168" s="8" t="inlineStr">
+        <is>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+        </is>
+      </c>
+      <c r="N168" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O168" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="20" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>Kontejnery suti tříděné</t>
+        </is>
+      </c>
+      <c r="D169" s="20" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+        </is>
+      </c>
+      <c r="F169" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H169" s="10" t="n"/>
+      <c r="I169" s="10" t="n"/>
+      <c r="J169" s="8" t="inlineStr">
+        <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K169" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L169" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M169" s="8" t="inlineStr">
+        <is>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+        </is>
+      </c>
+      <c r="N169" s="20" t="inlineStr">
+        <is>
+          <t>#9, #10</t>
+        </is>
+      </c>
+      <c r="O169" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>Doprava materiálu</t>
+        </is>
+      </c>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>031031000</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+        </is>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="10" t="n"/>
+      <c r="I170" s="10" t="n"/>
+      <c r="J170" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K170" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="L163" s="20" t="inlineStr">
+      <c r="L170" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M163" s="8" t="inlineStr">
+      <c r="M170" s="8" t="inlineStr">
+        <is>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
+        </is>
+      </c>
+      <c r="N170" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O170" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadů 56.9 t</t>
+        </is>
+      </c>
+      <c r="D171" s="20" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+        </is>
+      </c>
+      <c r="F171" s="20" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="H171" s="10" t="n"/>
+      <c r="I171" s="10" t="n"/>
+      <c r="J171" s="8" t="inlineStr">
+        <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K171" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L171" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M171" s="8" t="inlineStr">
+        <is>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+        </is>
+      </c>
+      <c r="N171" s="20" t="inlineStr">
+        <is>
+          <t>#9, #10</t>
+        </is>
+      </c>
+      <c r="O171" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="20" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické zaměření před + po realizaci</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+        </is>
+      </c>
+      <c r="F172" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G172" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" s="10" t="n"/>
+      <c r="I172" s="10" t="n"/>
+      <c r="J172" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K172" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L172" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M172" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet před+po pro každou stavbu</t>
+        </is>
+      </c>
+      <c r="N172" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O172" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="20" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Kolaudace</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>Kolaudační řízení</t>
+        </is>
+      </c>
+      <c r="D173" s="20" t="inlineStr">
+        <is>
+          <t>030171000</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+        </is>
+      </c>
+      <c r="F173" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G173" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" s="10" t="n"/>
+      <c r="I173" s="10" t="n"/>
+      <c r="J173" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K173" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L173" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M173" s="8" t="inlineStr">
+        <is>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+        </is>
+      </c>
+      <c r="N173" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O173" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="20" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Pojištění + zábory</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+        </is>
+      </c>
+      <c r="D174" s="20" t="inlineStr">
+        <is>
+          <t>030081000</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G174" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="10" t="n"/>
+      <c r="I174" s="10" t="n"/>
+      <c r="J174" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K174" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L174" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M174" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — pojistná povinnost</t>
+        </is>
+      </c>
+      <c r="N174" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O174" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="20" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Pojištění + zábory</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>Krátkodobé zábory ul. Fibichova</t>
+        </is>
+      </c>
+      <c r="D175" s="20" t="inlineStr">
+        <is>
+          <t>030083000</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+        </is>
+      </c>
+      <c r="F175" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="10" t="n"/>
+      <c r="I175" s="10" t="n"/>
+      <c r="J175" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K175" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L175" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M175" s="8" t="inlineStr">
+        <is>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+        </is>
+      </c>
+      <c r="N175" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O175" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="20" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Průzkumy</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>Mykologický průzkum dřeva při bourání</t>
+        </is>
+      </c>
+      <c r="D176" s="20" t="inlineStr">
+        <is>
+          <t>030131000</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>Mykologický průzkum stávajícího krovu a dřevěných trámů zhlaví — provádí autorizovaný mykolog při bourání</t>
+        </is>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G176" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" s="10" t="n"/>
+      <c r="I176" s="10" t="n"/>
+      <c r="J176" s="8" t="inlineStr">
+        <is>
+          <t>mykolog</t>
+        </is>
+      </c>
+      <c r="K176" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L176" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M176" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §3.2.3 — explicitně mykologický průzkum</t>
+        </is>
+      </c>
+      <c r="N176" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O176" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="20" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Průzkumy</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Azbestový průzkum podrobný před demolicí</t>
+        </is>
+      </c>
+      <c r="D177" s="20" t="inlineStr">
+        <is>
+          <t>030133000</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+        </is>
+      </c>
+      <c r="F177" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G177" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="10" t="n"/>
+      <c r="I177" s="10" t="n"/>
+      <c r="J177" s="8" t="inlineStr">
+        <is>
+          <t>azbestovy_specialista</t>
+        </is>
+      </c>
+      <c r="K177" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L177" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M177" s="8" t="inlineStr">
+        <is>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+        </is>
+      </c>
+      <c r="N177" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O177" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="20" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Revize</t>
+        </is>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>Revize hydrantu vnějšího</t>
+        </is>
+      </c>
+      <c r="D178" s="20" t="inlineStr">
+        <is>
+          <t>030161000</t>
+        </is>
+      </c>
+      <c r="E178" s="8" t="inlineStr">
+        <is>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G178" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="10" t="n"/>
+      <c r="I178" s="10" t="n"/>
+      <c r="J178" s="8" t="inlineStr">
+        <is>
+          <t>revize_specialista</t>
+        </is>
+      </c>
+      <c r="K178" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L178" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M178" s="8" t="inlineStr">
+        <is>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+        </is>
+      </c>
+      <c r="N178" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O178" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="20" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>Buňky kancelář + sociální</t>
+        </is>
+      </c>
+      <c r="D179" s="20" t="inlineStr">
+        <is>
+          <t>030011000</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+        </is>
+      </c>
+      <c r="F179" s="20" t="inlineStr">
+        <is>
+          <t>kpl-měs</t>
+        </is>
+      </c>
+      <c r="G179" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H179" s="10" t="n"/>
+      <c r="I179" s="10" t="n"/>
+      <c r="J179" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K179" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L179" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M179" s="8" t="inlineStr">
+        <is>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+        </is>
+      </c>
+      <c r="N179" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O179" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="20" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>Mobilní WC</t>
+        </is>
+      </c>
+      <c r="D180" s="20" t="inlineStr">
+        <is>
+          <t>030013000</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>ks-měs</t>
+        </is>
+      </c>
+      <c r="G180" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H180" s="10" t="n"/>
+      <c r="I180" s="10" t="n"/>
+      <c r="J180" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K180" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L180" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M180" s="8" t="inlineStr">
+        <is>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+        </is>
+      </c>
+      <c r="N180" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O180" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>El. odběr + vodovodní odběr stavby</t>
+        </is>
+      </c>
+      <c r="D181" s="20" t="inlineStr">
+        <is>
+          <t>031011000</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+        </is>
+      </c>
+      <c r="F181" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G181" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="10" t="n"/>
+      <c r="I181" s="10" t="n"/>
+      <c r="J181" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K181" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L181" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M181" s="8" t="inlineStr">
         <is>
           <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
-      <c r="N163" s="20" t="inlineStr">
+      <c r="N181" s="20" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="O163" s="26" t="inlineStr">
+      <c r="O181" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="20" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D182" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F182" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G182" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="10" t="n"/>
+      <c r="I182" s="10" t="n"/>
+      <c r="J182" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K182" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L182" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M182" s="8" t="inlineStr">
+        <is>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+        </is>
+      </c>
+      <c r="N182" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O182" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O163"/>
-  <conditionalFormatting sqref="K2:K163">
+  <autoFilter ref="A1:O182"/>
+  <conditionalFormatting sqref="K2:K182">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
